--- a/data/videos/eval/ground_truth.xlsx
+++ b/data/videos/eval/ground_truth.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ghiffaryr\iseql\multimodal-surveillance-iseql\data\videos\eval2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ghiffaryr\iseql\multimodal-surveillance-iseql\data\videos\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22600B52-AA06-4812-AA75-A2091C4E5E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3EA2F1-589B-4BE1-94AC-7A89C41AAE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Expected Events" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="111">
   <si>
     <t>scene</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>vehicle_collision</t>
-  </si>
-  <si>
-    <t>loitering</t>
   </si>
   <si>
     <t>handoff</t>
@@ -975,13 +972,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -989,13 +986,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1003,13 +1000,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1017,13 +1014,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1031,13 +1028,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1045,13 +1042,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1161,13 +1158,13 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -1175,13 +1172,13 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -1189,13 +1186,13 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1203,13 +1200,13 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1221,31 +1218,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="8.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>16</v>
-      </c>
-      <c r="H1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1256,7 +1256,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>1.5</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1284,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>36</v>
@@ -1301,7 +1301,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1312,7 +1312,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>38</v>
@@ -1329,7 +1329,7 @@
         <v>5.625</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1340,7 +1340,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>1.8333333333333333</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1368,7 +1368,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>44</v>
@@ -1385,7 +1385,7 @@
         <v>5.125</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1396,7 +1396,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>48</v>
@@ -1413,7 +1413,7 @@
         <v>6.625</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1424,7 +1424,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>2.1666666666666665</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1452,7 +1452,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1469,7 +1469,7 @@
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1480,7 +1480,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>61</v>
@@ -1497,7 +1497,7 @@
         <v>2.9166666666666665</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1525,7 +1525,7 @@
         <v>4.375</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1553,7 +1553,7 @@
         <v>6.666666666666667</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1564,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -1581,7 +1581,7 @@
         <v>4.708333333333333</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>118</v>
@@ -1609,7 +1609,7 @@
         <v>6.666666666666667</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1620,7 +1620,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15">
         <v>126</v>
@@ -1637,7 +1637,7 @@
         <v>7.625</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1665,7 +1665,7 @@
         <v>3.2083333333333335</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1676,7 +1676,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17">
         <v>63</v>
@@ -1693,7 +1693,7 @@
         <v>2.9166666666666665</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1704,7 +1704,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>70</v>
@@ -1721,7 +1721,7 @@
         <v>8.0416666666666661</v>
       </c>
       <c r="H18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -1749,7 +1749,7 @@
         <v>5.75</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -1760,7 +1760,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>107</v>
@@ -1777,7 +1777,7 @@
         <v>5.916666666666667</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -1788,7 +1788,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>126</v>
@@ -1805,7 +1805,7 @@
         <v>6.958333333333333</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -1833,7 +1833,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -1844,7 +1844,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>16</v>
@@ -1861,7 +1861,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -1872,7 +1872,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>71</v>
@@ -1889,7 +1889,7 @@
         <v>9.6666666666666661</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -1917,7 +1917,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="H25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -1928,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>40</v>
@@ -1945,7 +1945,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -1956,7 +1956,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>134</v>
@@ -1973,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -1984,7 +1984,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28">
         <v>93</v>
@@ -2001,7 +2001,7 @@
         <v>5.5</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -2012,7 +2012,7 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29">
         <v>132</v>
@@ -2029,7 +2029,7 @@
         <v>8.6666666666666661</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -2040,7 +2040,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         <v>1.4166666666666667</v>
       </c>
       <c r="H30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -2068,7 +2068,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31">
         <v>35</v>
@@ -2085,7 +2085,7 @@
         <v>3.375</v>
       </c>
       <c r="H31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32">
         <v>95</v>
@@ -2113,7 +2113,7 @@
         <v>7.875</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -2124,7 +2124,7 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33">
         <v>189</v>
@@ -2141,7 +2141,7 @@
         <v>9.0833333333333339</v>
       </c>
       <c r="H33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -2152,7 +2152,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>2.1666666666666665</v>
       </c>
       <c r="H34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -2180,7 +2180,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D35">
         <v>53</v>
@@ -2197,7 +2197,7 @@
         <v>3.375</v>
       </c>
       <c r="H35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -2208,7 +2208,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D36">
         <v>88</v>
@@ -2225,7 +2225,7 @@
         <v>7.041666666666667</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -2236,7 +2236,7 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37">
         <v>169</v>
@@ -2253,7 +2253,7 @@
         <v>9.1666666666666661</v>
       </c>
       <c r="H37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -2264,7 +2264,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2281,7 +2281,7 @@
         <v>1.7916666666666667</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -2292,7 +2292,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D39">
         <v>44</v>
@@ -2309,7 +2309,7 @@
         <v>4.333333333333333</v>
       </c>
       <c r="H39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -2320,7 +2320,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D40">
         <v>19</v>
@@ -2337,7 +2337,7 @@
         <v>3.0416666666666665</v>
       </c>
       <c r="H40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -2348,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D41">
         <v>73</v>
@@ -2373,7 +2373,7 @@
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42">
         <v>79</v>
@@ -2390,7 +2390,7 @@
         <v>4.541666666666667</v>
       </c>
       <c r="H42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -2418,7 +2418,7 @@
         <v>10</v>
       </c>
       <c r="H43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -2429,7 +2429,7 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D44">
         <v>31</v>
@@ -2446,7 +2446,7 @@
         <v>2.2083333333333335</v>
       </c>
       <c r="H44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D45">
         <v>53</v>
@@ -2482,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D46">
         <v>63</v>
@@ -2499,7 +2499,7 @@
         <v>5.416666666666667</v>
       </c>
       <c r="H46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -2527,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="H47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -2538,7 +2538,7 @@
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D48">
         <v>30</v>
@@ -2555,7 +2555,7 @@
         <v>3.0833333333333335</v>
       </c>
       <c r="H48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -2566,7 +2566,7 @@
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D49">
         <v>53</v>
@@ -2591,7 +2591,7 @@
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D50">
         <v>74</v>
@@ -2608,7 +2608,7 @@
         <v>4.583333333333333</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -2636,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="H51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -2647,24 +2647,24 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52">
+        <v>48</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H52" t="s">
         <v>74</v>
-      </c>
-      <c r="D52">
-        <v>51</v>
-      </c>
-      <c r="E52">
-        <v>119</v>
-      </c>
-      <c r="F52">
-        <f t="shared" si="0"/>
-        <v>2.125</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="1"/>
-        <v>4.958333333333333</v>
-      </c>
-      <c r="H52" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -2675,7 +2675,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D53">
         <v>54</v>
@@ -2692,7 +2692,7 @@
         <v>6.458333333333333</v>
       </c>
       <c r="H53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -2703,7 +2703,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D54">
         <v>82</v>
@@ -2720,7 +2720,7 @@
         <v>7.083333333333333</v>
       </c>
       <c r="H54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -2731,7 +2731,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         <v>4.625</v>
       </c>
       <c r="H55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -2759,7 +2759,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D56">
         <v>111</v>
@@ -2776,7 +2776,7 @@
         <v>8.2916666666666661</v>
       </c>
       <c r="H56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -2787,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D57">
         <v>10</v>
@@ -2804,7 +2804,7 @@
         <v>5.5</v>
       </c>
       <c r="H57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -2815,7 +2815,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D58">
         <v>120</v>
@@ -2832,7 +2832,7 @@
         <v>9.75</v>
       </c>
       <c r="H58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
@@ -2843,7 +2843,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2860,7 +2860,7 @@
         <v>2.5833333333333335</v>
       </c>
       <c r="H59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
@@ -2871,7 +2871,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D60">
         <v>54</v>
@@ -2888,7 +2888,7 @@
         <v>5.291666666666667</v>
       </c>
       <c r="H60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
@@ -2899,7 +2899,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61">
         <v>116</v>
@@ -2916,7 +2916,7 @@
         <v>7.208333333333333</v>
       </c>
       <c r="H61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -2927,7 +2927,7 @@
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>1.4583333333333333</v>
       </c>
       <c r="H62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -2955,7 +2955,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D63">
         <v>36</v>
@@ -2972,7 +2972,7 @@
         <v>1.5416666666666667</v>
       </c>
       <c r="H63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
@@ -2983,7 +2983,7 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D64">
         <v>50</v>
@@ -3000,7 +3000,7 @@
         <v>2.1666666666666665</v>
       </c>
       <c r="H64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
@@ -3011,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65">
         <v>37</v>
@@ -3028,7 +3028,7 @@
         <v>5.5</v>
       </c>
       <c r="H65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
@@ -3039,7 +3039,7 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D66">
         <v>4</v>
@@ -3056,7 +3056,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="H66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -3067,7 +3067,7 @@
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D67">
         <v>10</v>
@@ -3084,7 +3084,7 @@
         <v>5.083333333333333</v>
       </c>
       <c r="H67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -3095,7 +3095,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D68">
         <v>10</v>
@@ -3112,7 +3112,7 @@
         <v>5.416666666666667</v>
       </c>
       <c r="H68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
@@ -3123,7 +3123,7 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D69">
         <v>108</v>
@@ -3140,7 +3140,7 @@
         <v>5.75</v>
       </c>
       <c r="H69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
@@ -3151,7 +3151,7 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D70">
         <v>138</v>
@@ -3168,7 +3168,7 @@
         <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
@@ -3179,7 +3179,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3196,7 +3196,7 @@
         <v>1.875</v>
       </c>
       <c r="H71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
@@ -3207,7 +3207,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D72">
         <v>47</v>
@@ -3224,7 +3224,7 @@
         <v>4.041666666666667</v>
       </c>
       <c r="H72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
@@ -3235,7 +3235,7 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D73">
         <v>103</v>
@@ -3252,7 +3252,7 @@
         <v>5.75</v>
       </c>
       <c r="H73" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -3263,7 +3263,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D74">
         <v>138</v>
@@ -3280,7 +3280,7 @@
         <v>7.583333333333333</v>
       </c>
       <c r="H74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -3291,7 +3291,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3308,7 +3308,7 @@
         <v>2</v>
       </c>
       <c r="H75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -3319,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D76">
         <v>49</v>
@@ -3336,7 +3336,7 @@
         <v>4.125</v>
       </c>
       <c r="H76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -3347,7 +3347,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D77">
         <v>28</v>
@@ -3364,7 +3364,7 @@
         <v>2.5833333333333335</v>
       </c>
       <c r="H77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
@@ -3375,7 +3375,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D78">
         <v>63</v>
@@ -3392,7 +3392,7 @@
         <v>4.291666666666667</v>
       </c>
       <c r="H78" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -3420,7 +3420,7 @@
         <v>10</v>
       </c>
       <c r="H79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
@@ -3431,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3448,7 +3448,7 @@
         <v>2.0833333333333335</v>
       </c>
       <c r="H80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
@@ -3459,7 +3459,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D81">
         <v>50</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="H81" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
@@ -3504,7 +3504,7 @@
         <v>10</v>
       </c>
       <c r="H82" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
@@ -3515,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D83">
         <v>57</v>
@@ -3532,7 +3532,7 @@
         <v>6.625</v>
       </c>
       <c r="H83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
@@ -3543,7 +3543,7 @@
         <v>2</v>
       </c>
       <c r="C84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D84">
         <v>40</v>
@@ -3560,7 +3560,7 @@
         <v>6.916666666666667</v>
       </c>
       <c r="H84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
@@ -3571,7 +3571,7 @@
         <v>2</v>
       </c>
       <c r="C85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>5.083333333333333</v>
       </c>
       <c r="H85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
@@ -3599,7 +3599,7 @@
         <v>2</v>
       </c>
       <c r="C86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86">
         <v>111</v>
@@ -3616,7 +3616,7 @@
         <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
@@ -3627,7 +3627,7 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>5.166666666666667</v>
       </c>
       <c r="H87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
@@ -3655,7 +3655,7 @@
         <v>2</v>
       </c>
       <c r="C88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D88">
         <v>115</v>
@@ -3672,7 +3672,7 @@
         <v>7.916666666666667</v>
       </c>
       <c r="H88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
